--- a/doc/examples/forecasting/forecast-method.xlsx
+++ b/doc/examples/forecasting/forecast-method.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\jdetaeye\workspace\frepple-community\doc\examples\forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B535567C-DCC1-4165-9491-BE77F2393D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851C1D9-EF2B-462D-A633-FDE7331B535A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="757" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2362,9 +2362,6 @@
     <t>plan.solver</t>
   </si>
   <si>
-    <t>distribution</t>
-  </si>
-  <si>
     <t>Selects the solver to generate the plan. Possible choices are "heuristic" and "distribution".</t>
   </si>
   <si>
@@ -2576,6 +2573,9 @@
   </si>
   <si>
     <t>if(cost != 0, orderstotal := newvalue /cost, orderstotalvalue := newvalue)</t>
+  </si>
+  <si>
+    <t>heuristic</t>
   </si>
 </sst>
 </file>
@@ -2585,7 +2585,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2933,7 +2933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G550"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="50.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -2944,7 +2944,7 @@
     <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>78</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>79</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>82</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>86</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>89</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>90</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>92</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>93</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>96</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>100</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>102</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>103</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>106</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>107</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>109</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>110</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>112</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>113</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>122</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>132</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>133</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>134</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>135</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>136</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>137</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>138</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>140</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>141</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>142</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>143</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>146</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>147</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>148</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>149</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>150</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>151</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>152</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>153</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>155</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>156</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>157</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>158</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>159</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>160</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>161</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>163</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>164</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>165</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>166</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>167</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>168</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>169</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>170</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>171</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>172</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>173</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>174</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>175</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7">
       <c r="A163" t="s">
         <v>177</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>178</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7">
       <c r="A165" t="s">
         <v>179</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>180</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>181</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>182</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>184</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>185</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>186</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>187</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>188</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>189</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>190</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>191</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>192</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>193</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>194</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>195</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>196</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>197</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>198</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7">
       <c r="A186" t="s">
         <v>200</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7">
       <c r="A187" t="s">
         <v>201</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7">
       <c r="A188" t="s">
         <v>202</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7">
       <c r="A189" t="s">
         <v>203</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7">
       <c r="A190" t="s">
         <v>204</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7">
       <c r="A191" t="s">
         <v>205</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7">
       <c r="A192" t="s">
         <v>206</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7">
       <c r="A193" t="s">
         <v>207</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7">
       <c r="A194" t="s">
         <v>208</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7">
       <c r="A195" t="s">
         <v>209</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7">
       <c r="A196" t="s">
         <v>210</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7">
       <c r="A197" t="s">
         <v>211</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>212</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7">
       <c r="A199" t="s">
         <v>213</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7">
       <c r="A200" t="s">
         <v>214</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7">
       <c r="A201" t="s">
         <v>215</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7">
       <c r="A202" t="s">
         <v>216</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7">
       <c r="A203" t="s">
         <v>217</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7">
       <c r="A204" t="s">
         <v>218</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7">
       <c r="A205" t="s">
         <v>219</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7">
       <c r="A206" t="s">
         <v>220</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7">
       <c r="A207" t="s">
         <v>221</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7">
       <c r="A208" t="s">
         <v>222</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7">
       <c r="A209" t="s">
         <v>223</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7">
       <c r="A210" t="s">
         <v>224</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7">
       <c r="A211" t="s">
         <v>225</v>
       </c>
@@ -7797,7 +7797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7">
       <c r="A212" t="s">
         <v>226</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7">
       <c r="A213" t="s">
         <v>227</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7">
       <c r="A214" t="s">
         <v>228</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7">
       <c r="A215" t="s">
         <v>229</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7">
       <c r="A216" t="s">
         <v>230</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7">
       <c r="A217" t="s">
         <v>231</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7">
       <c r="A218" t="s">
         <v>232</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
         <v>233</v>
       </c>
@@ -7981,7 +7981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
         <v>234</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
         <v>235</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>236</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
         <v>237</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>238</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7">
       <c r="A225" t="s">
         <v>239</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>240</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>241</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7">
       <c r="A228" t="s">
         <v>242</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7">
       <c r="A229" t="s">
         <v>243</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7">
       <c r="A230" t="s">
         <v>244</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>245</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>246</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7">
       <c r="A233" t="s">
         <v>247</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7">
       <c r="A234" t="s">
         <v>248</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7">
       <c r="A235" t="s">
         <v>249</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7">
       <c r="A236" t="s">
         <v>250</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7">
       <c r="A237" t="s">
         <v>251</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7">
       <c r="A238" t="s">
         <v>252</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7">
       <c r="A239" t="s">
         <v>253</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7">
       <c r="A240" t="s">
         <v>254</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7">
       <c r="A241" t="s">
         <v>255</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7">
       <c r="A242" t="s">
         <v>256</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7">
       <c r="A243" t="s">
         <v>257</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7">
       <c r="A244" t="s">
         <v>258</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>259</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7">
       <c r="A246" t="s">
         <v>260</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7">
       <c r="A247" t="s">
         <v>261</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7">
       <c r="A248" t="s">
         <v>262</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7">
       <c r="A249" t="s">
         <v>263</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7">
       <c r="A250" t="s">
         <v>264</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7">
       <c r="A251" t="s">
         <v>265</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7">
       <c r="A252" t="s">
         <v>266</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7">
       <c r="A253" t="s">
         <v>267</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7">
       <c r="A254" t="s">
         <v>268</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7">
       <c r="A255" t="s">
         <v>269</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>270</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>271</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>272</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>273</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>274</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>275</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>276</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>277</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>278</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>279</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>280</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>281</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>282</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>283</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>284</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>285</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>286</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>287</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>288</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>289</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>290</v>
       </c>
@@ -9292,7 +9292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>291</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>292</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>293</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>294</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>295</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>296</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>297</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>298</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>299</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>300</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>301</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>302</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>303</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>304</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>305</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>306</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>307</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>308</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>309</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>310</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
         <v>311</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
         <v>312</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
         <v>313</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
         <v>314</v>
       </c>
@@ -9844,7 +9844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
         <v>315</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7">
       <c r="A302" t="s">
         <v>316</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7">
       <c r="A303" t="s">
         <v>317</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
         <v>318</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
         <v>319</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
         <v>320</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7">
       <c r="A307" t="s">
         <v>321</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
         <v>322</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7">
       <c r="A309" t="s">
         <v>323</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7">
       <c r="A310" t="s">
         <v>324</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7">
       <c r="A311" t="s">
         <v>325</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7">
       <c r="A312" t="s">
         <v>326</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7">
       <c r="A313" t="s">
         <v>327</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7">
       <c r="A314" t="s">
         <v>328</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7">
       <c r="A315" t="s">
         <v>329</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7">
       <c r="A316" t="s">
         <v>330</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7">
       <c r="A317" t="s">
         <v>331</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7">
       <c r="A318" t="s">
         <v>332</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7">
       <c r="A319" t="s">
         <v>333</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7">
       <c r="A320" t="s">
         <v>334</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7">
       <c r="A321" t="s">
         <v>335</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7">
       <c r="A322" t="s">
         <v>336</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7">
       <c r="A323" t="s">
         <v>339</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7">
       <c r="A324" t="s">
         <v>340</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7">
       <c r="A325" t="s">
         <v>341</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7">
       <c r="A326" t="s">
         <v>342</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7">
       <c r="A327" t="s">
         <v>343</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7">
       <c r="A328" t="s">
         <v>344</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7">
       <c r="A329" t="s">
         <v>345</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7">
       <c r="A330" t="s">
         <v>346</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7">
       <c r="A331" t="s">
         <v>347</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7">
       <c r="A332" t="s">
         <v>348</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7">
       <c r="A333" t="s">
         <v>349</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7">
       <c r="A334" t="s">
         <v>350</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7">
       <c r="A335" t="s">
         <v>351</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7">
       <c r="A336" t="s">
         <v>352</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7">
       <c r="A337" t="s">
         <v>353</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7">
       <c r="A338" t="s">
         <v>354</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7">
       <c r="A339" t="s">
         <v>355</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7">
       <c r="A340" t="s">
         <v>356</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7">
       <c r="A341" t="s">
         <v>357</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7">
       <c r="A342" t="s">
         <v>358</v>
       </c>
@@ -10810,7 +10810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7">
       <c r="A343" t="s">
         <v>359</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7">
       <c r="A344" t="s">
         <v>360</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7">
       <c r="A345" t="s">
         <v>361</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7">
       <c r="A346" t="s">
         <v>362</v>
       </c>
@@ -10902,7 +10902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7">
       <c r="A347" t="s">
         <v>363</v>
       </c>
@@ -10925,7 +10925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7">
       <c r="A348" t="s">
         <v>364</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7">
       <c r="A349" t="s">
         <v>365</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7">
       <c r="A350" t="s">
         <v>366</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7">
       <c r="A351" t="s">
         <v>367</v>
       </c>
@@ -11017,7 +11017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7">
       <c r="A352" t="s">
         <v>368</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7">
       <c r="A353" t="s">
         <v>369</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7">
       <c r="A354" t="s">
         <v>370</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7">
       <c r="A355" t="s">
         <v>371</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7">
       <c r="A356" t="s">
         <v>372</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7">
       <c r="A357" t="s">
         <v>373</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7">
       <c r="A358" t="s">
         <v>374</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7">
       <c r="A359" t="s">
         <v>375</v>
       </c>
@@ -11201,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7">
       <c r="A360" t="s">
         <v>376</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7">
       <c r="A361" t="s">
         <v>377</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7">
       <c r="A362" t="s">
         <v>378</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7">
       <c r="A363" t="s">
         <v>379</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7">
       <c r="A364" t="s">
         <v>380</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7">
       <c r="A365" t="s">
         <v>381</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7">
       <c r="A366" t="s">
         <v>382</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7">
       <c r="A367" t="s">
         <v>383</v>
       </c>
@@ -11385,7 +11385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7">
       <c r="A368" t="s">
         <v>384</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7">
       <c r="A369" t="s">
         <v>385</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7">
       <c r="A370" t="s">
         <v>386</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7">
       <c r="A371" t="s">
         <v>387</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7">
       <c r="A372" t="s">
         <v>388</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7">
       <c r="A373" t="s">
         <v>389</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7">
       <c r="A374" t="s">
         <v>390</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7">
       <c r="A375" t="s">
         <v>391</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7">
       <c r="A376" t="s">
         <v>392</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7">
       <c r="A377" t="s">
         <v>393</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7">
       <c r="A378" t="s">
         <v>394</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7">
       <c r="A379" t="s">
         <v>395</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7">
       <c r="A380" t="s">
         <v>396</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7">
       <c r="A381" t="s">
         <v>397</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7">
       <c r="A382" t="s">
         <v>398</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:7">
       <c r="A383" t="s">
         <v>399</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:7">
       <c r="A384" t="s">
         <v>400</v>
       </c>
@@ -11776,7 +11776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7">
       <c r="A385" t="s">
         <v>401</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7">
       <c r="A386" t="s">
         <v>402</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7">
       <c r="A387" t="s">
         <v>403</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7">
       <c r="A388" t="s">
         <v>404</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7">
       <c r="A389" t="s">
         <v>405</v>
       </c>
@@ -11891,7 +11891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:7">
       <c r="A390" t="s">
         <v>406</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7">
       <c r="A391" t="s">
         <v>407</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7">
       <c r="A392" t="s">
         <v>408</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7">
       <c r="A393" t="s">
         <v>409</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7">
       <c r="A394" t="s">
         <v>410</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:7">
       <c r="A395" t="s">
         <v>411</v>
       </c>
@@ -12029,7 +12029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7">
       <c r="A396" t="s">
         <v>412</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7">
       <c r="A397" t="s">
         <v>413</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7">
       <c r="A398" t="s">
         <v>414</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7">
       <c r="A399" t="s">
         <v>415</v>
       </c>
@@ -12121,7 +12121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7">
       <c r="A400" t="s">
         <v>416</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7">
       <c r="A401" t="s">
         <v>417</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7">
       <c r="A402" t="s">
         <v>418</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7">
       <c r="A403" t="s">
         <v>419</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7">
       <c r="A404" t="s">
         <v>420</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:7">
       <c r="A405" t="s">
         <v>421</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7">
       <c r="A406" t="s">
         <v>422</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7">
       <c r="A407" t="s">
         <v>423</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:7">
       <c r="A408" t="s">
         <v>424</v>
       </c>
@@ -12328,7 +12328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7">
       <c r="A409" t="s">
         <v>425</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7">
       <c r="A410" t="s">
         <v>426</v>
       </c>
@@ -12374,7 +12374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7">
       <c r="A411" t="s">
         <v>427</v>
       </c>
@@ -12397,7 +12397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7">
       <c r="A412" t="s">
         <v>428</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7">
       <c r="A413" t="s">
         <v>429</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7">
       <c r="A414" t="s">
         <v>430</v>
       </c>
@@ -12466,7 +12466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7">
       <c r="A415" t="s">
         <v>431</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7">
       <c r="A416" t="s">
         <v>432</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7">
       <c r="A417" t="s">
         <v>433</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7">
       <c r="A418" t="s">
         <v>434</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7">
       <c r="A419" t="s">
         <v>435</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7">
       <c r="A420" t="s">
         <v>436</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7">
       <c r="A421" t="s">
         <v>437</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7">
       <c r="A422" t="s">
         <v>438</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7">
       <c r="A423" t="s">
         <v>439</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7">
       <c r="A424" t="s">
         <v>440</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7">
       <c r="A425" t="s">
         <v>441</v>
       </c>
@@ -12719,7 +12719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7">
       <c r="A426" t="s">
         <v>442</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7">
       <c r="A427" t="s">
         <v>443</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7">
       <c r="A428" t="s">
         <v>444</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7">
       <c r="A429" t="s">
         <v>445</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7">
       <c r="A430" t="s">
         <v>446</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7">
       <c r="A431" t="s">
         <v>447</v>
       </c>
@@ -12857,7 +12857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7">
       <c r="A432" t="s">
         <v>448</v>
       </c>
@@ -12880,7 +12880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7">
       <c r="A433" t="s">
         <v>449</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7">
       <c r="A434" t="s">
         <v>450</v>
       </c>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7">
       <c r="A435" t="s">
         <v>451</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7">
       <c r="A436" t="s">
         <v>452</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7">
       <c r="A437" t="s">
         <v>453</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7">
       <c r="A438" t="s">
         <v>454</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7">
       <c r="A439" t="s">
         <v>455</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7">
       <c r="A440" t="s">
         <v>456</v>
       </c>
@@ -13064,7 +13064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7">
       <c r="A441" t="s">
         <v>457</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7">
       <c r="A442" t="s">
         <v>458</v>
       </c>
@@ -13110,7 +13110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7">
       <c r="A443" t="s">
         <v>459</v>
       </c>
@@ -13133,7 +13133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7">
       <c r="A444" t="s">
         <v>460</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7">
       <c r="A445" t="s">
         <v>461</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7">
       <c r="A446" t="s">
         <v>462</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7">
       <c r="A447" t="s">
         <v>463</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7">
       <c r="A448" t="s">
         <v>464</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7">
       <c r="A449" t="s">
         <v>465</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7">
       <c r="A450" t="s">
         <v>466</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7">
       <c r="A451" t="s">
         <v>467</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7">
       <c r="A452" t="s">
         <v>468</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7">
       <c r="A453" t="s">
         <v>469</v>
       </c>
@@ -13363,7 +13363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7">
       <c r="A454" t="s">
         <v>470</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7">
       <c r="A455" t="s">
         <v>471</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7">
       <c r="A456" t="s">
         <v>472</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7">
       <c r="A457" t="s">
         <v>473</v>
       </c>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7">
       <c r="A458" t="s">
         <v>474</v>
       </c>
@@ -13478,7 +13478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7">
       <c r="A459" t="s">
         <v>475</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7">
       <c r="A460" t="s">
         <v>476</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7">
       <c r="A461" t="s">
         <v>477</v>
       </c>
@@ -13547,7 +13547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:7">
       <c r="A462" t="s">
         <v>478</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:7">
       <c r="A463" t="s">
         <v>479</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7">
       <c r="A464" t="s">
         <v>480</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:7">
       <c r="A465" t="s">
         <v>481</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:7">
       <c r="A466" t="s">
         <v>482</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:7">
       <c r="A467" t="s">
         <v>483</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:7">
       <c r="A468" t="s">
         <v>484</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:7">
       <c r="A469" t="s">
         <v>485</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:7">
       <c r="A470" t="s">
         <v>486</v>
       </c>
@@ -13754,7 +13754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:7">
       <c r="A471" t="s">
         <v>487</v>
       </c>
@@ -13777,7 +13777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:7">
       <c r="A472" t="s">
         <v>488</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:7">
       <c r="A473" t="s">
         <v>489</v>
       </c>
@@ -13823,7 +13823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:7">
       <c r="A474" t="s">
         <v>490</v>
       </c>
@@ -13846,7 +13846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:7">
       <c r="A475" t="s">
         <v>491</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:7">
       <c r="A476" t="s">
         <v>492</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:7">
       <c r="A477" t="s">
         <v>493</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:7">
       <c r="A478" t="s">
         <v>494</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:7">
       <c r="A479" t="s">
         <v>495</v>
       </c>
@@ -13961,7 +13961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:7">
       <c r="A480" t="s">
         <v>496</v>
       </c>
@@ -13984,7 +13984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7">
       <c r="A481" t="s">
         <v>497</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7">
       <c r="A482" t="s">
         <v>498</v>
       </c>
@@ -14030,7 +14030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7">
       <c r="A483" t="s">
         <v>500</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7">
       <c r="A484" t="s">
         <v>501</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:7">
       <c r="A485" t="s">
         <v>502</v>
       </c>
@@ -14099,7 +14099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7">
       <c r="A486" t="s">
         <v>503</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7">
       <c r="A487" t="s">
         <v>504</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7">
       <c r="A488" t="s">
         <v>505</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:7">
       <c r="A489" t="s">
         <v>506</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7">
       <c r="A490" t="s">
         <v>507</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7">
       <c r="A491" t="s">
         <v>508</v>
       </c>
@@ -14237,7 +14237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7">
       <c r="A492" t="s">
         <v>509</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:7">
       <c r="A493" t="s">
         <v>510</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7">
       <c r="A494" t="s">
         <v>511</v>
       </c>
@@ -14306,7 +14306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7">
       <c r="A495" t="s">
         <v>512</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7">
       <c r="A496" t="s">
         <v>513</v>
       </c>
@@ -14352,7 +14352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7">
       <c r="A497" t="s">
         <v>514</v>
       </c>
@@ -14375,7 +14375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7">
       <c r="A498" t="s">
         <v>515</v>
       </c>
@@ -14398,7 +14398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7">
       <c r="A499" t="s">
         <v>516</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7">
       <c r="A500" t="s">
         <v>517</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:7">
       <c r="A501" t="s">
         <v>518</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7">
       <c r="A502" t="s">
         <v>519</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7">
       <c r="A503" t="s">
         <v>520</v>
       </c>
@@ -14513,7 +14513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:7">
       <c r="A504" t="s">
         <v>521</v>
       </c>
@@ -14536,7 +14536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7">
       <c r="A505" t="s">
         <v>522</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:7">
       <c r="A506" t="s">
         <v>523</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:7">
       <c r="A507" t="s">
         <v>524</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7">
       <c r="A508" t="s">
         <v>525</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7">
       <c r="A509" t="s">
         <v>526</v>
       </c>
@@ -14651,7 +14651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7">
       <c r="A510" t="s">
         <v>527</v>
       </c>
@@ -14674,7 +14674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7">
       <c r="A511" t="s">
         <v>528</v>
       </c>
@@ -14697,7 +14697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7">
       <c r="A512" t="s">
         <v>529</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7">
       <c r="A513" t="s">
         <v>530</v>
       </c>
@@ -14743,7 +14743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7">
       <c r="A514" t="s">
         <v>531</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7">
       <c r="A515" t="s">
         <v>532</v>
       </c>
@@ -14789,7 +14789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7">
       <c r="A516" t="s">
         <v>533</v>
       </c>
@@ -14812,7 +14812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7">
       <c r="A517" t="s">
         <v>534</v>
       </c>
@@ -14835,7 +14835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:7">
       <c r="A518" t="s">
         <v>535</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:7">
       <c r="A519" t="s">
         <v>536</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7">
       <c r="A520" t="s">
         <v>537</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7">
       <c r="A521" t="s">
         <v>538</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7">
       <c r="A522" t="s">
         <v>539</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7">
       <c r="A523" t="s">
         <v>540</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7">
       <c r="A524" t="s">
         <v>541</v>
       </c>
@@ -14996,7 +14996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:7">
       <c r="A525" t="s">
         <v>542</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7">
       <c r="A526" t="s">
         <v>543</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:7">
       <c r="A527" t="s">
         <v>544</v>
       </c>
@@ -15065,7 +15065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:7">
       <c r="A528" t="s">
         <v>545</v>
       </c>
@@ -15088,7 +15088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:7">
       <c r="A529" t="s">
         <v>546</v>
       </c>
@@ -15111,7 +15111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:7">
       <c r="A530" t="s">
         <v>547</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:7">
       <c r="A531" t="s">
         <v>548</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:7">
       <c r="A532" t="s">
         <v>549</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:7">
       <c r="A533" t="s">
         <v>550</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:7">
       <c r="A534" t="s">
         <v>551</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:7">
       <c r="A535" t="s">
         <v>552</v>
       </c>
@@ -15249,7 +15249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:7">
       <c r="A536" t="s">
         <v>553</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:7">
       <c r="A537" t="s">
         <v>554</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:7">
       <c r="A538" t="s">
         <v>555</v>
       </c>
@@ -15318,7 +15318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:7">
       <c r="A539" t="s">
         <v>556</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:7">
       <c r="A540" t="s">
         <v>557</v>
       </c>
@@ -15364,7 +15364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:7">
       <c r="A541" t="s">
         <v>558</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:7">
       <c r="A542" t="s">
         <v>559</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:7">
       <c r="A543" t="s">
         <v>560</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:7">
       <c r="A544" t="s">
         <v>561</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:7">
       <c r="A545" t="s">
         <v>562</v>
       </c>
@@ -15479,7 +15479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:7">
       <c r="A546" t="s">
         <v>563</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:7">
       <c r="A547" t="s">
         <v>564</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:7">
       <c r="A548" t="s">
         <v>565</v>
       </c>
@@ -15548,7 +15548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:7">
       <c r="A549" t="s">
         <v>566</v>
       </c>
@@ -15571,7 +15571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:7">
       <c r="A550" t="s">
         <v>567</v>
       </c>
@@ -15603,64 +15603,64 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC87E9B3-F41F-4824-A07C-84834131B726}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>765</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>585</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>770</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>771</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>772</v>
       </c>
-      <c r="E2" t="s">
-        <v>773</v>
-      </c>
       <c r="F2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -15672,27 +15672,27 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>773</v>
+      </c>
+      <c r="L2" t="s">
         <v>774</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>776</v>
       </c>
-      <c r="B3" t="s">
-        <v>777</v>
-      </c>
       <c r="D3" t="s">
+        <v>771</v>
+      </c>
+      <c r="E3" t="s">
         <v>772</v>
       </c>
-      <c r="E3" t="s">
-        <v>773</v>
-      </c>
       <c r="F3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -15704,27 +15704,27 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>777</v>
+      </c>
+      <c r="L3" t="s">
         <v>778</v>
       </c>
-      <c r="L3" t="s">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>780</v>
       </c>
-      <c r="B4" t="s">
-        <v>781</v>
-      </c>
       <c r="D4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E4" t="s">
         <v>772</v>
       </c>
-      <c r="E4" t="s">
-        <v>773</v>
-      </c>
       <c r="F4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -15736,27 +15736,27 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>781</v>
+      </c>
+      <c r="L4" t="s">
         <v>782</v>
       </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>784</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>771</v>
+      </c>
+      <c r="E5" t="s">
+        <v>772</v>
+      </c>
+      <c r="F5" t="s">
         <v>785</v>
-      </c>
-      <c r="D5" t="s">
-        <v>772</v>
-      </c>
-      <c r="E5" t="s">
-        <v>773</v>
-      </c>
-      <c r="F5" t="s">
-        <v>786</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -15768,30 +15768,30 @@
         <v>-1</v>
       </c>
       <c r="K5" t="s">
+        <v>786</v>
+      </c>
+      <c r="L5" t="s">
         <v>787</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
         <v>788</v>
       </c>
-      <c r="M5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>789</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>771</v>
+      </c>
+      <c r="E6" t="s">
         <v>790</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>772</v>
-      </c>
-      <c r="E6" t="s">
-        <v>791</v>
-      </c>
-      <c r="F6" t="s">
-        <v>773</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -15803,59 +15803,59 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
+        <v>791</v>
+      </c>
+      <c r="L6" t="s">
         <v>792</v>
       </c>
-      <c r="L6" t="s">
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>794</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>795</v>
       </c>
-      <c r="C7" t="s">
-        <v>796</v>
-      </c>
       <c r="D7" t="s">
+        <v>771</v>
+      </c>
+      <c r="E7" t="s">
         <v>772</v>
       </c>
-      <c r="E7" t="s">
-        <v>773</v>
-      </c>
       <c r="F7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>799</v>
       </c>
-      <c r="B8" t="s">
-        <v>800</v>
-      </c>
       <c r="D8" t="s">
+        <v>771</v>
+      </c>
+      <c r="E8" t="s">
         <v>772</v>
       </c>
-      <c r="E8" t="s">
-        <v>773</v>
-      </c>
       <c r="F8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -15867,56 +15867,56 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
+        <v>800</v>
+      </c>
+      <c r="L8" t="s">
         <v>801</v>
       </c>
-      <c r="L8" t="s">
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>803</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>804</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>805</v>
       </c>
-      <c r="D9" t="s">
-        <v>806</v>
-      </c>
       <c r="E9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
+        <v>806</v>
+      </c>
+      <c r="B10" t="s">
         <v>807</v>
       </c>
-      <c r="B10" t="s">
-        <v>808</v>
-      </c>
       <c r="D10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E10" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -15928,27 +15928,27 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
+        <v>808</v>
+      </c>
+      <c r="L10" t="s">
         <v>809</v>
       </c>
-      <c r="L10" t="s">
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>811</v>
       </c>
-      <c r="B11" t="s">
-        <v>812</v>
-      </c>
       <c r="D11" t="s">
+        <v>771</v>
+      </c>
+      <c r="E11" t="s">
         <v>772</v>
       </c>
-      <c r="E11" t="s">
-        <v>773</v>
-      </c>
       <c r="F11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -15963,27 +15963,27 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
+        <v>812</v>
+      </c>
+      <c r="L11" t="s">
         <v>813</v>
       </c>
-      <c r="L11" t="s">
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>815</v>
       </c>
-      <c r="B12" t="s">
-        <v>816</v>
-      </c>
       <c r="D12" t="s">
+        <v>771</v>
+      </c>
+      <c r="E12" t="s">
+        <v>790</v>
+      </c>
+      <c r="F12" t="s">
         <v>772</v>
-      </c>
-      <c r="E12" t="s">
-        <v>791</v>
-      </c>
-      <c r="F12" t="s">
-        <v>773</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -15995,27 +15995,27 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
+        <v>816</v>
+      </c>
+      <c r="L12" t="s">
         <v>817</v>
       </c>
-      <c r="L12" t="s">
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>819</v>
       </c>
-      <c r="B13" t="s">
-        <v>820</v>
-      </c>
       <c r="D13" t="s">
+        <v>771</v>
+      </c>
+      <c r="E13" t="s">
         <v>772</v>
       </c>
-      <c r="E13" t="s">
-        <v>773</v>
-      </c>
       <c r="F13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -16027,10 +16027,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
+        <v>820</v>
+      </c>
+      <c r="L13" t="s">
         <v>821</v>
-      </c>
-      <c r="L13" t="s">
-        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -16043,7 +16043,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -16052,7 +16052,7 @@
     <col min="5" max="5" width="6.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>569</v>
       </c>
@@ -16077,7 +16077,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>571</v>
       </c>
@@ -16088,7 +16088,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>572</v>
       </c>
@@ -16099,7 +16099,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>337</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>499</v>
       </c>
@@ -16176,14 +16176,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>578</v>
       </c>
@@ -16202,7 +16202,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>580</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -16224,7 +16224,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>338</v>
       </c>
@@ -16244,14 +16244,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -16265,7 +16265,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="40.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -16275,7 +16275,7 @@
     <col min="6" max="7" width="8.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>586</v>
       </c>
@@ -16321,7 +16321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>588</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>589</v>
       </c>
@@ -16367,7 +16367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>590</v>
       </c>
@@ -16399,7 +16399,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.90625" bestFit="1" customWidth="1"/>
@@ -16407,7 +16407,7 @@
     <col min="4" max="4" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>337</v>
       </c>
@@ -16449,7 +16449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>499</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>337</v>
       </c>
@@ -16505,7 +16505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>176</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>499</v>
       </c>
@@ -16542,12 +16542,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16555,7 +16555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>595</v>
       </c>
@@ -16563,7 +16563,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>596</v>
       </c>
@@ -16580,7 +16580,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
@@ -16592,7 +16592,7 @@
     <col min="8" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>176</v>
       </c>
@@ -16667,7 +16667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>499</v>
       </c>
@@ -16690,7 +16690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>337</v>
       </c>
@@ -16725,14 +16725,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="44.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="182.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>600</v>
       </c>
@@ -16754,29 +16754,29 @@
         <v>602</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>603</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C3" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>599</v>
       </c>
       <c r="C4" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>605</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>608</v>
       </c>
@@ -16798,7 +16798,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>611</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>614</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>617</v>
       </c>
@@ -16831,7 +16831,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>620</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>623</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>626</v>
       </c>
@@ -16864,7 +16864,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>629</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>631</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>633</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>635</v>
       </c>
@@ -16908,7 +16908,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>638</v>
       </c>
@@ -16919,7 +16919,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>641</v>
       </c>
@@ -16930,7 +16930,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>644</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>646</v>
       </c>
@@ -16952,7 +16952,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>649</v>
       </c>
@@ -16963,7 +16963,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>652</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>655</v>
       </c>
@@ -16985,7 +16985,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>658</v>
       </c>
@@ -16996,7 +16996,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>661</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>663</v>
       </c>
@@ -17018,7 +17018,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>665</v>
       </c>
@@ -17029,7 +17029,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>667</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>670</v>
       </c>
@@ -17051,7 +17051,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>672</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>674</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>676</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>678</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>680</v>
       </c>
@@ -17106,7 +17106,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>682</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>685</v>
       </c>
@@ -17128,7 +17128,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>687</v>
       </c>
@@ -17139,7 +17139,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>690</v>
       </c>
@@ -17150,7 +17150,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>692</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>695</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>696</v>
       </c>
@@ -17183,7 +17183,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>699</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>700</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>701</v>
       </c>
@@ -17216,7 +17216,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>702</v>
       </c>
@@ -17227,7 +17227,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>704</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>707</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>710</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>712</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>715</v>
       </c>
@@ -17282,7 +17282,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>717</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>719</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>721</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>723</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>726</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>729</v>
       </c>
@@ -17348,7 +17348,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>732</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>734</v>
       </c>
@@ -17370,7 +17370,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>737</v>
       </c>
@@ -17381,7 +17381,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>739</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>742</v>
       </c>
@@ -17403,7 +17403,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>744</v>
       </c>
@@ -17414,7 +17414,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>746</v>
       </c>
@@ -17425,7 +17425,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>748</v>
       </c>
@@ -17436,37 +17436,37 @@
         <v>749</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>750</v>
       </c>
       <c r="B65" t="s">
+        <v>822</v>
+      </c>
+      <c r="C65" t="s">
         <v>751</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>752</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>753</v>
       </c>
       <c r="B66" t="s">
         <v>599</v>
       </c>
       <c r="C66" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>754</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>755</v>
       </c>
       <c r="B67" t="s">
         <v>599</v>
       </c>
       <c r="C67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
